--- a/output/pdf_financials_xlsx/HO.P.xlsx
+++ b/output/pdf_financials_xlsx/HO.P.xlsx
@@ -2522,19 +2522,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.293</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.043378</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.329991</v>
       </c>
     </row>
     <row r="93">
@@ -3830,7 +3830,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4308,7 +4312,11 @@
           <t>Reserves (Note 5)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.037</v>
       </c>

--- a/output/pdf_financials_xlsx/HO.P.xlsx
+++ b/output/pdf_financials_xlsx/HO.P.xlsx
@@ -669,19 +669,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000156</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.09617199999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.226226</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.234748</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.147991</v>
       </c>
     </row>
     <row r="13">
@@ -1027,19 +1027,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.150255</v>
+        <v>-0.150411</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.005708</v>
+        <v>-0.090464</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.124454</v>
+        <v>-0.101772</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.08358500000000001</v>
+        <v>-0.318333</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.4274</v>
+        <v>-0.575391</v>
       </c>
     </row>
     <row r="28">
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.150255</v>
+        <v>-0.150411</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.005708</v>
+        <v>-0.090464</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.124454</v>
+        <v>-0.101772</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.08358500000000001</v>
+        <v>-0.318333</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.4274</v>
+        <v>-0.575391</v>
       </c>
     </row>
     <row r="30">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
